--- a/healthcare_forms/005_diabetes_monitoring_form--healthcare_forms.xlsx
+++ b/healthcare_forms/005_diabetes_monitoring_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Diet</t>
+          <t>Diet Frequency</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Exercise Frequency</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Weight Frequency</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Weight Time</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1204,24 +1204,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mmHg</t>
+          <t>mmhg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blood_pressure_unit_choices</t>
+          <t>weight_unit_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mmhg</t>
+          <t>lbs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mmhg</t>
+          <t>lbs</t>
         </is>
       </c>
     </row>
@@ -1233,46 +1233,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>weight_unit_choices</t>
+          <t>medication_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>weight_unit_choices</t>
+          <t>medication_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lbs</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1284,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>morning_and_night</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Morning and Night</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medication_frequency_choices</t>
+          <t>diet_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medication_frequency_choices</t>
+          <t>diet_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>morning_and_night</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morning and Night</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1335,80 +1335,80 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>diet_frequency_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lunch</t>
+          <t>10_minutes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lunch</t>
+          <t>10 minutes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>diet_frequency_choices</t>
+          <t>exercise_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dinner</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exercise_frequency_choices</t>
+          <t>blood_sugar_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10_minutes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10 minutes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exercise_frequency_choices</t>
+          <t>blood_sugar_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30_minutes</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30 minutes</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1420,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blood_sugar_frequency_choices</t>
+          <t>weight_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blood_sugar_frequency_choices</t>
+          <t>weight_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1471,44 +1471,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>weight_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>weight_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
